--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/8924-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/8924-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{189C5A13-EF56-403D-A244-18E6960C6620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{108CEE4C-CFC5-43CA-BE10-CC6FF97C7255}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{99CAFD35-B560-419D-AA7C-A908F5352DB7}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{F65FB6CD-39B6-4B4F-8370-A8D6F3DF51A4}"/>
   </bookViews>
   <sheets>
     <sheet name="8924-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1514,27 +1514,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{056CA89D-DDE0-4215-BACB-785FD93EB28C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFB4FA3C-4136-4291-9F82-A40886CD72CF}">
   <dimension ref="A1:X35"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1568,7 +1567,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1604,7 +1603,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1656,7 +1655,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1724,7 +1723,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2024</v>
       </c>
@@ -1796,7 +1795,7 @@
         <v>8.58</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39">
         <v>2023</v>
       </c>
@@ -1868,7 +1867,7 @@
         <v>5.91</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>2022</v>
       </c>
@@ -1940,7 +1939,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="39">
         <v>2021</v>
       </c>
@@ -2012,7 +2011,7 @@
         <v>15.4</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="37">
         <v>2020</v>
       </c>
@@ -2084,7 +2083,7 @@
         <v>8.76</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="39">
         <v>2019</v>
       </c>
@@ -2156,7 +2155,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="37">
         <v>2018</v>
       </c>
@@ -2228,7 +2227,7 @@
         <v>6.82</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="39">
         <v>2017</v>
       </c>
@@ -2300,7 +2299,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="37">
         <v>2016</v>
       </c>
@@ -2372,7 +2371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="39">
         <v>2015</v>
       </c>
@@ -2444,7 +2443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="37">
         <v>2014</v>
       </c>
@@ -2516,7 +2515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="39">
         <v>2013</v>
       </c>
@@ -2588,7 +2587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="37">
         <v>2012</v>
       </c>
@@ -2660,7 +2659,7 @@
         <v>2.92</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="39">
         <v>2011</v>
       </c>
@@ -2732,7 +2731,7 @@
         <v>3.58</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="37">
         <v>2010</v>
       </c>
@@ -2804,7 +2803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="39">
         <v>2009</v>
       </c>
@@ -2876,7 +2875,7 @@
         <v>6.61</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="37">
         <v>2008</v>
       </c>
@@ -2948,7 +2947,7 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="39">
         <v>2007</v>
       </c>
@@ -3020,7 +3019,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="37">
         <v>2006</v>
       </c>
@@ -3092,7 +3091,7 @@
         <v>9.3800000000000008</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="39">
         <v>2005</v>
       </c>
@@ -3164,7 +3163,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="37">
         <v>2004</v>
       </c>
@@ -3236,7 +3235,7 @@
         <v>9.75</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="39">
         <v>2003</v>
       </c>
@@ -3308,7 +3307,7 @@
         <v>7.09</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="41">
         <v>2002</v>
       </c>
@@ -3380,7 +3379,7 @@
         <v>7.12</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="43"/>
       <c r="B28" s="44"/>
       <c r="C28" s="20" t="s">
@@ -3408,7 +3407,7 @@
       <c r="W28" s="50"/>
       <c r="X28" s="46"/>
     </row>
-    <row r="29" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="39">
         <v>2001</v>
       </c>
@@ -3480,7 +3479,7 @@
         <v>7.04</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="37">
         <v>2000</v>
       </c>
@@ -3552,7 +3551,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="39">
         <v>1999</v>
       </c>
@@ -3624,7 +3623,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="37">
         <v>1998</v>
       </c>
@@ -3696,7 +3695,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="39">
         <v>1997</v>
       </c>
@@ -3768,7 +3767,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="37">
         <v>1996</v>
       </c>
@@ -3840,7 +3839,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="39" t="s">
         <v>50</v>
       </c>
